--- a/WPF/DevExpress.HybridApp.Wpf/CS/DevExpress.HybridApp.Wpf/Resources/Analysis/ProductAnalysis.xlsx
+++ b/WPF/DevExpress.HybridApp.Wpf/CS/DevExpress.HybridApp.Wpf/Resources/Analysis/ProductAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VCS\2020.1\Demos.RealLife\DevExpress.OutlookInspiredApp\DevExpress.OutlookInspiredApp.Win\Resources\Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\2025.2\Demos.RealLife\DevExpress.OutlookInspiredApp\DevExpress.OutlookInspiredApp.Win\Resources\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B804EC-067E-482F-B551-5748A0E905E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F5BFC6-2F19-480C-8FBF-CCCE662A1F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28030" yWindow="-9220" windowWidth="26300" windowHeight="16170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Financial Report" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Financial Report'!$B$2:$L$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Financial Data'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Financial Report'!$17:$17</definedName>
+    <definedName name="ReportYear">YEAR(TODAY())-1</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,6 +35,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -528,19 +551,19 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -565,16 +588,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -589,22 +612,22 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -613,7 +636,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -634,10 +657,10 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -753,40 +776,40 @@
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Oct</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>Nov</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>Dec</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Sep</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -873,40 +896,40 @@
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Oct</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>Nov</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>Dec</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Sep</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -993,40 +1016,40 @@
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Oct</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>Nov</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>Dec</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Sep</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1113,40 +1136,40 @@
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Oct</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>Nov</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>Dec</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Sep</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1298,9 +1321,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2000529</xdr:colOff>
+      <xdr:colOff>2009419</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>428705</xdr:rowOff>
+      <xdr:rowOff>423625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1734,46 +1757,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:L37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" customWidth="1"/>
-    <col min="9" max="9" width="3.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.6640625" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="3.6640625" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="3.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
+    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="47" t="str">
-        <f ca="1">CONCATENATE("REVENUE ANALYSIS ", YEAR(TODAY())-1)</f>
-        <v>REVENUE ANALYSIS 2019</v>
+      <c r="H3" s="47" t="str" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">CONCATENATE("REVENUE ANALYSIS ", ReportYear)</f>
+        <v>REVENUE ANALYSIS 2025</v>
       </c>
       <c r="I3" s="47"/>
       <c r="J3" s="47"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
     </row>
-    <row r="4" spans="2:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="39" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:12" s="4" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:12" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17" t="s">
         <v>1</v>
       </c>
@@ -1796,7 +1819,7 @@
       <c r="K6" s="49"/>
       <c r="L6" s="50"/>
     </row>
-    <row r="7" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="41">
         <f>SUM('Financial Data'!H31:H42)</f>
         <v>0</v>
@@ -1824,23 +1847,23 @@
       <c r="K7" s="52"/>
       <c r="L7" s="53"/>
     </row>
-    <row r="15" spans="2:12" ht="54" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="54" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="25"/>
       <c r="C17" s="26"/>
-      <c r="D17" s="54" t="str">
-        <f ca="1">CONCATENATE("FY ", YEAR(TODAY())-3)</f>
-        <v>FY 2017</v>
+      <c r="D17" s="54" t="str" cm="1">
+        <f t="array" aca="1" ref="D17" ca="1">CONCATENATE("FY ", ReportYear-2)</f>
+        <v>FY 2023</v>
       </c>
       <c r="E17" s="54"/>
-      <c r="F17" s="55" t="str">
-        <f ca="1">CONCATENATE("FY ", YEAR(TODAY())-2)</f>
-        <v>FY 2018</v>
+      <c r="F17" s="55" t="str" cm="1">
+        <f t="array" aca="1" ref="F17" ca="1">CONCATENATE("FY ", ReportYear-1)</f>
+        <v>FY 2024</v>
       </c>
       <c r="G17" s="55"/>
-      <c r="H17" s="55" t="str">
-        <f ca="1">CONCATENATE("FY ", YEAR(TODAY())-1)</f>
-        <v>FY 2019</v>
+      <c r="H17" s="55" t="str" cm="1">
+        <f t="array" aca="1" ref="H17" ca="1">CONCATENATE("FY ", ReportYear)</f>
+        <v>FY 2025</v>
       </c>
       <c r="I17" s="55"/>
       <c r="J17" s="26"/>
@@ -1849,7 +1872,7 @@
       </c>
       <c r="L17" s="56"/>
     </row>
-    <row r="18" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>7</v>
       </c>
@@ -1876,7 +1899,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="31" t="s">
         <v>8</v>
       </c>
@@ -1903,7 +1926,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="21" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1953,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="31" t="s">
         <v>10</v>
       </c>
@@ -1957,7 +1980,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="21" t="s">
         <v>11</v>
       </c>
@@ -1984,7 +2007,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="31" t="s">
         <v>12</v>
       </c>
@@ -2011,7 +2034,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="21" t="s">
         <v>13</v>
       </c>
@@ -2038,7 +2061,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="31" t="s">
         <v>14</v>
       </c>
@@ -2065,7 +2088,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="21" t="s">
         <v>15</v>
       </c>
@@ -2092,7 +2115,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="31" t="s">
         <v>16</v>
       </c>
@@ -2119,7 +2142,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="21" t="s">
         <v>17</v>
       </c>
@@ -2146,7 +2169,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="31" t="s">
         <v>18</v>
       </c>
@@ -2173,7 +2196,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="21" t="s">
         <v>19</v>
       </c>
@@ -2200,7 +2223,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="31" t="s">
         <v>20</v>
       </c>
@@ -2227,7 +2250,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="21" t="s">
         <v>21</v>
       </c>
@@ -2254,7 +2277,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="31" t="s">
         <v>22</v>
       </c>
@@ -2281,7 +2304,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="21" t="s">
         <v>23</v>
       </c>
@@ -2308,7 +2331,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="31" t="s">
         <v>24</v>
       </c>
@@ -2335,7 +2358,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="21" t="s">
         <v>25</v>
       </c>
@@ -2362,7 +2385,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="2:12" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="35" t="s">
         <v>41</v>
       </c>
@@ -2471,25 +2494,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{14141D86-C1BE-41BB-BE05-18A41377EC61}">
-            <x14:iconSet iconSet="3Arrows" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>J18:J37</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="9" id="{300098D9-579E-47CC-AA6C-4C218E681D71}">
             <x14:iconSet iconSet="3Arrows" custom="1">
@@ -2585,6 +2589,25 @@
           </x14:cfRule>
           <xm:sqref>J7</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="10" id="{14141D86-C1BE-41BB-BE05-18A41377EC61}">
+            <x14:iconSet iconSet="3Arrows" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>J18:J37</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -2597,35 +2620,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:H42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="8" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="8" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:8" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:8" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="40" t="str">
-        <f ca="1">CONCATENATE("REVENUE ANALYSIS ", YEAR(TODAY())-1)</f>
-        <v>REVENUE ANALYSIS 2019</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="40" t="str" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">CONCATENATE("REVENUE ANALYSIS ", ReportYear)</f>
+        <v>REVENUE ANALYSIS 2025</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="2:8" s="4" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" s="4" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
@@ -2648,13 +2671,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
-        <f ca="1">YEAR(TODAY())-3</f>
-        <v>2017</v>
+    <row r="7" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">ReportYear-2</f>
+        <v>2023</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D7" s="10">
         <v>0</v>
@@ -2673,10 +2696,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="12">
         <v>0</v>
@@ -2695,10 +2718,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D9" s="10">
         <v>0</v>
@@ -2717,10 +2740,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
       <c r="C10" s="11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D10" s="12">
         <v>0</v>
@@ -2739,10 +2762,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8"/>
       <c r="C11" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2761,10 +2784,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="12">
         <v>0</v>
@@ -2783,10 +2806,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" s="10">
         <v>0</v>
@@ -2805,10 +2828,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" s="12">
         <v>0</v>
@@ -2827,10 +2850,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="8"/>
       <c r="C15" s="9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
@@ -2849,10 +2872,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D16" s="12">
         <v>0</v>
@@ -2871,10 +2894,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D17" s="10">
         <v>0</v>
@@ -2893,10 +2916,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D18" s="12">
         <v>0</v>
@@ -2915,13 +2938,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="8">
-        <f ca="1">YEAR(TODAY())-2</f>
-        <v>2018</v>
+    <row r="19" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="8" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">ReportYear-1</f>
+        <v>2024</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D19" s="10">
         <v>0</v>
@@ -2940,10 +2963,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D20" s="12">
         <v>0</v>
@@ -2962,10 +2985,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D21" s="10">
         <v>0</v>
@@ -2984,10 +3007,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D22" s="12">
         <v>0</v>
@@ -3006,10 +3029,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D23" s="10">
         <v>0</v>
@@ -3028,10 +3051,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="11"/>
       <c r="C24" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" s="12">
         <v>0</v>
@@ -3050,10 +3073,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" s="10">
         <v>0</v>
@@ -3072,10 +3095,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11"/>
       <c r="C26" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D26" s="12">
         <v>0</v>
@@ -3094,10 +3117,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D27" s="10">
         <v>0</v>
@@ -3116,10 +3139,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="11"/>
       <c r="C28" s="11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D28" s="12">
         <v>0</v>
@@ -3138,10 +3161,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8"/>
       <c r="C29" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D29" s="10">
         <v>0</v>
@@ -3160,10 +3183,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11"/>
       <c r="C30" s="11" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D30" s="12">
         <v>0</v>
@@ -3182,13 +3205,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="8">
-        <f ca="1">YEAR(TODAY())-1</f>
-        <v>2019</v>
+    <row r="31" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" cm="1">
+        <f t="array" aca="1" ref="B31" ca="1">ReportYear</f>
+        <v>2025</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D31" s="10">
         <v>0</v>
@@ -3207,10 +3230,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="11"/>
       <c r="C32" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D32" s="12">
         <v>0</v>
@@ -3229,10 +3252,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8"/>
       <c r="C33" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D33" s="10">
         <v>0</v>
@@ -3251,10 +3274,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="11"/>
       <c r="C34" s="11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D34" s="12">
         <v>0</v>
@@ -3273,10 +3296,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8"/>
       <c r="C35" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D35" s="10">
         <v>0</v>
@@ -3295,10 +3318,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="11"/>
       <c r="C36" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D36" s="12">
         <v>0</v>
@@ -3317,10 +3340,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8"/>
       <c r="C37" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D37" s="10">
         <v>0</v>
@@ -3339,10 +3362,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="11"/>
       <c r="C38" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D38" s="12">
         <v>0</v>
@@ -3361,10 +3384,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8"/>
       <c r="C39" s="9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D39" s="10">
         <v>0</v>
@@ -3383,10 +3406,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="11"/>
       <c r="C40" s="11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D40" s="12">
         <v>0</v>
@@ -3405,10 +3428,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="8"/>
       <c r="C41" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D41" s="10">
         <v>0</v>
@@ -3427,10 +3450,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="13"/>
       <c r="C42" s="13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D42" s="7">
         <v>0</v>
